--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/los-rios.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/los-rios.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>6924.83</v>
+        <v>6847.68</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>3840.79</v>
+        <v>3834.84</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>3102.21</v>
+        <v>3019.15</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>11490.65</v>
+        <v>11588.18</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>3099.4</v>
+        <v>3055.41</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>1240.3</v>
+        <v>1225.87</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>3007.56</v>
+        <v>2990.89</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/los-rios.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/los-rios.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Los Ríos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Los Ríos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4923-154-CM25</t>
+          <t>3568-98-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.200.700-k</t>
+          <t>69.201.200-3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FUTRONO</t>
+          <t>I MUNICIPALIDAD DE PANGUIPULLI</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ADM SPA.</t>
+          <t>MAX EDUARDO SARAVIA SUÁREZ</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>77.909.208-9</t>
+          <t>13.962.630-3</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>6847.68</v>
+        <v>2582.79</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3568-1042-CM25</t>
+          <t>3568-185-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>3834.84</v>
+        <v>2786.03</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3568-278-CM26</t>
+          <t>3568-291-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>3019.15</v>
+        <v>2697.34</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4923-7-CM26</t>
+          <t>3568-449-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,27 +707,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.200.700-k</t>
+          <t>69.201.200-3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FUTRONO</t>
+          <t>I MUNICIPALIDAD DE PANGUIPULLI</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ADM SPA.</t>
+          <t>MAX EDUARDO SARAVIA SUÁREZ</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>77.909.208-9</t>
+          <t>13.962.630-3</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>11588.18</v>
+        <v>2805.66</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3568-404-CM26</t>
+          <t>3568-536-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>3055.41</v>
+        <v>2841.52</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4230-117-CM26</t>
+          <t>4923-83-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,27 +829,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>69.200.700-k</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Valdivia</t>
+          <t>I MUNICIPALIDAD DE FUTRONO</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
+          <t>ADM SPA.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>76.730.550-8</t>
+          <t>77.909.208-9</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>1225.87</v>
+        <v>10124.64</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3568-504-CM26</t>
+          <t>3568-557-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -935,7 +935,678 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
+        <v>3822.61</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1057553-1723-CM25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>61.607.509-8</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE L</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Hales Hnos y Cia Ltda</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>83.535.000-2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>5853.63</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>3568-742-CM25</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>69.201.200-3</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PANGUIPULLI</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>MAX EDUARDO SARAVIA SUÁREZ</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>13.962.630-3</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>2717.99</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>3568-874-CM25</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>69.201.200-3</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PANGUIPULLI</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>MAX EDUARDO SARAVIA SUÁREZ</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>13.962.630-3</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>3843.16</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>4923-154-CM25</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>69.200.700-k</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE FUTRONO</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ADM SPA.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>77.909.208-9</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>6847.68</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>3568-1042-CM25</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>69.201.200-3</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PANGUIPULLI</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>MAX EDUARDO SARAVIA SUÁREZ</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>13.962.630-3</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>3834.84</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>3568-278-CM26</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>69.201.200-3</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PANGUIPULLI</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>MAX EDUARDO SARAVIA SUÁREZ</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>13.962.630-3</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>3019.15</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>4923-7-CM26</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>69.200.700-k</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE FUTRONO</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ADM SPA.</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>77.909.208-9</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>11588.18</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>3568-404-CM26</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>69.201.200-3</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PANGUIPULLI</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>MAX EDUARDO SARAVIA SUÁREZ</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>13.962.630-3</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>3055.41</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>4230-117-CM26</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>60.505.523-0</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Carabineros de Chile - Prefectura Valdivia</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>76.730.550-8</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>1225.87</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>3568-504-CM26</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>69.201.200-3</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PANGUIPULLI</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>MAX EDUARDO SARAVIA SUÁREZ</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>13.962.630-3</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="n">
         <v>2990.89</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>4923-21-CM26</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>69.200.700-k</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE FUTRONO</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ADM SPA.</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>77.909.208-9</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>17188.63</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/los-rios.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/los-rios.xlsx
@@ -1449,7 +1449,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Valdivia</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">

--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/los-rios.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/los-rios.xlsx
@@ -867,7 +867,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1176,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1363,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1611,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/los-rios.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/los-rios.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1625,6 +1625,67 @@
         <v>17188.63</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>3568-679-CM26</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>69.201.200-3</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PANGUIPULLI</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>MAX EDUARDO SARAVIA SUÁREZ</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>13.962.630-3</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>3114.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
